--- a/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_2_Oct_v2_94.xlsx
+++ b/reports/acdr2026_staff_deployment/動態表ACDR2026_as_of_2_Oct_v2_94.xlsx
@@ -9074,11 +9074,6 @@
       <c r="AA9" s="94" t="n"/>
       <c r="AB9" s="94" t="n"/>
       <c r="AC9" s="95" t="n"/>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>sk_da06052da0c0227daf6db024942a34fa6f8a6428b003c6da</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="107">
       <c r="A10" s="40">
